--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G408"/>
+  <dimension ref="A1:G412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1148,22 +1148,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1183,22 +1183,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1218,22 +1218,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1253,22 +1253,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1323,26 +1323,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1393,26 +1393,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1428,22 +1428,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Employment Change QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY 2nd EstQ4</t>
+          <t>Employment Change YoY PrelQ4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Employment Change QoQ PrelQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1599,22 +1599,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Employment Change YoY PrelQ4</t>
+          <t>GDP Growth Rate YoY 2nd EstQ4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1768,31 +1768,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1808,18 +1804,18 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -1839,18 +1835,18 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1870,22 +1866,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1931,23 +1931,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2067,23 +2071,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2098,12 +2102,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2113,16 +2117,16 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2138,26 +2142,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -2173,26 +2173,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2208,22 +2204,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2243,22 +2239,26 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2274,22 +2274,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2309,18 +2309,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2433,22 +2433,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -2468,22 +2468,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -2575,19 +2575,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Vehicle Sales YoYJAN</t>
+          <t>Wholesale Prices YoYJAN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2605,18 +2605,18 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2629,23 +2629,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Vehicle Sales YoYJAN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -2663,14 +2659,18 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wholesale Prices YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2688,18 +2688,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GDP Price Index YoY PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2715,22 +2719,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDP Private Consumption QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2746,18 +2750,18 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -2777,22 +2781,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -2808,22 +2812,18 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP Price Index YoY PrelQ4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -2839,18 +2839,18 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP Private Consumption QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>BCB Focus Market Readout</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -3532,12 +3532,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -3555,21 +3555,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Auto Production YoYJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
         <v>2</v>
       </c>
@@ -3582,21 +3578,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Auto Sales YoYJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
         <v>2</v>
       </c>
@@ -3609,19 +3601,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>TRY-150.0B</t>
+          <t>$-24.0B</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -3636,19 +3628,19 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Auto Production YoYJAN</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>$-24.0B</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -3663,17 +3655,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Auto Sales YoYJAN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
       <c r="G108" t="n">
         <v>2</v>
       </c>
@@ -3686,17 +3682,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>TRY-150.0B</t>
+        </is>
+      </c>
       <c r="G109" t="n">
         <v>2</v>
       </c>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BCB Focus Market Readout</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -3929,22 +3929,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Claimant Count ChangeJAN</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>7.0K</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -3960,22 +3960,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -3991,18 +3991,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Average Earnings incl. Bonus (3Mo/Yr)DEC</t>
+          <t>Employment ChangeDEC</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>5.9%</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-130K</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -4022,18 +4018,18 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Employment ChangeDEC</t>
+          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-130K</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -4049,14 +4045,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Average Earnings excl. Bonus (3Mo/Yr)DEC</t>
+          <t>HMRC Payrolls ChangeJAN</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-55.0K</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -4076,14 +4072,18 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HMRC Payrolls ChangeJAN</t>
+          <t>Claimant Count ChangeJAN</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-55.0K</t>
+          <t>7.0K</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -4134,22 +4134,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -4196,22 +4196,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -4222,23 +4222,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Unemployment RateQ4</t>
+          <t>Labour Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -4249,19 +4249,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Unemployed PersonsQ4</t>
+          <t>Labour Productivity QoQ FinalQ3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>8.1M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4299,27 +4303,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ FinalQ3</t>
+          <t>Unemployment RateQ4</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -4330,19 +4330,19 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ PrelQ4</t>
+          <t>Unemployed PersonsQ4</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>8.1M</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -4492,27 +4492,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -4523,27 +4523,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CPI Trimmed-Mean YoYJAN</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -4559,18 +4559,18 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>CPI Trimmed-Mean YoYJAN</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -4617,18 +4617,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -4671,22 +4675,18 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -4871,14 +4871,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
@@ -4894,14 +4894,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -5036,22 +5036,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>¥-2104B</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>¥-1400.0B</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -5067,18 +5067,18 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Machinery Orders MoMDEC</t>
+          <t>Exports YoYJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -5098,18 +5098,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Machinery Orders MoMDEC</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -5129,22 +5129,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>¥-2104B</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>¥-1400.0B</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -5160,22 +5160,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Exports YoYJAN</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -5380,18 +5380,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Retail Price Index YoYJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5438,14 +5434,18 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>PPI Input MoMJAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -5465,18 +5465,18 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>Retail Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -5523,18 +5523,18 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PPI Input MoMJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -5817,18 +5817,18 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5844,14 +5844,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -5871,18 +5871,18 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -5893,23 +5893,19 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="F190" t="inlineStr"/>
       <c r="G190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -5920,19 +5916,23 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -6317,22 +6317,18 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
@@ -6348,22 +6344,18 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -6379,18 +6371,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -6406,18 +6402,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -6582,17 +6582,21 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>20-Year Bond Auction</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
       <c r="G217" t="n">
         <v>3</v>
       </c>
@@ -6605,12 +6609,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual Budget Speech</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -6628,21 +6632,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>Annual Budget Speech</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>85.5</t>
-        </is>
-      </c>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="n">
         <v>3</v>
       </c>
@@ -6710,18 +6710,18 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
@@ -6737,18 +6737,18 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224">
@@ -6883,22 +6883,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230">
@@ -6914,22 +6914,18 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>20K</t>
-        </is>
-      </c>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231">
@@ -6972,18 +6968,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -6999,22 +6999,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>20K</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -7084,16 +7084,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Current AccountQ4</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>$ -0.6B</t>
-        </is>
-      </c>
+      <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
         <v>3</v>
       </c>
@@ -7111,12 +7107,16 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Current AccountQ4</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>$ -0.6B</t>
+        </is>
+      </c>
       <c r="G237" t="n">
         <v>3</v>
       </c>
@@ -7129,19 +7129,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceFEB</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -7187,19 +7187,19 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>5-Year OAT Auction</t>
+          <t>4-Year OAT Auction</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>4-Year OAT Auction</t>
+          <t>5-Year OAT Auction</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -7406,17 +7406,21 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
       <c r="G249" t="n">
         <v>3</v>
       </c>
@@ -7429,27 +7433,19 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>-25</t>
-        </is>
-      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -7483,23 +7479,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -7833,23 +7833,19 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -7896,18 +7892,18 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Raw Materials Prices MoMJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -7923,14 +7919,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -7945,23 +7941,27 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -7977,18 +7977,18 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>Raw Materials Prices MoMJAN</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -8004,18 +8004,18 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -8107,27 +8107,19 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Consumer Confidence FlashFEB</t>
+          <t>Monetary Policy Meeting Minutes</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>-14</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>-14.4</t>
-        </is>
-      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -8138,19 +8130,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Monetary Policy Meeting Minutes</t>
+          <t>Consumer Confidence FlashFEB</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>-14</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>-14.4</t>
+        </is>
+      </c>
       <c r="G277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -8552,12 +8552,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>30-Year TIPS Auction</t>
+          <t>6-Month LTN Auction</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -8575,21 +8575,17 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Central Government DebtJAN</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>TRY 9.4T</t>
-        </is>
-      </c>
+      <c r="F296" t="inlineStr"/>
       <c r="G296" t="n">
         <v>3</v>
       </c>
@@ -8625,12 +8621,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>30-Year TIPS Auction</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -8648,17 +8644,21 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>6-Month LTN Auction</t>
+          <t>Central Government DebtJAN</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>TRY 9.4T</t>
+        </is>
+      </c>
       <c r="G299" t="n">
         <v>3</v>
       </c>
@@ -8776,14 +8776,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -8798,17 +8798,21 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="G305" t="n">
         <v>2</v>
       </c>
@@ -8821,21 +8825,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
       <c r="G306" t="n">
         <v>2</v>
       </c>
@@ -8880,18 +8880,18 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309">
@@ -8907,22 +8907,18 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
@@ -8938,18 +8934,22 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8965,18 +8965,18 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -9131,14 +9131,14 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>HSBC Services PMI FlashFEB</t>
+          <t>HSBC Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -9185,14 +9185,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>HSBC Composite PMI FlashFEB</t>
+          <t>HSBC Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -9212,14 +9212,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Retail Sales ex Fuel YoYJAN</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -9239,14 +9239,18 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel YoYJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>£20.5B</t>
+        </is>
+      </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -9266,18 +9270,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>£20.5B</t>
-        </is>
-      </c>
+      <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -9432,18 +9432,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -9463,14 +9459,18 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -9521,22 +9521,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -9579,22 +9579,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -9610,22 +9610,22 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -9641,22 +9641,22 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -9734,18 +9734,18 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -9765,18 +9765,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+      <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -9796,14 +9792,18 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -9958,14 +9958,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>Economic Activity YoYDEC</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -9985,22 +9985,18 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="348">
@@ -10016,18 +10012,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Economic Activity YoYDEC</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="349">
@@ -10294,18 +10294,18 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -10325,18 +10325,18 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -10418,22 +10418,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
@@ -10476,22 +10476,22 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Federal Tax RevenuesJAN</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -10571,21 +10571,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>FDI (YTD) YoYJAN</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>-18.0%</t>
-        </is>
-      </c>
+      <c r="F368" t="inlineStr"/>
       <c r="G368" t="n">
         <v>3</v>
       </c>
@@ -10598,17 +10594,21 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>FDI (YTD) YoYJAN</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
       <c r="G369" t="n">
         <v>3</v>
       </c>
@@ -10621,12 +10621,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Federal Tax RevenuesJAN</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -10774,14 +10774,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Capacity UtilizationFEB</t>
+          <t>Business ConfidenceFEB</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="377">
@@ -10797,14 +10797,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Business ConfidenceFEB</t>
+          <t>Capacity UtilizationFEB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
       <c r="G377" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -10820,18 +10820,18 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Ifo Business ClimateFEB</t>
+          <t>Ifo ExpectationsFEB</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -10847,18 +10847,18 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Ifo Current ConditionsFEB</t>
+          <t>Ifo Business ClimateFEB</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -10874,14 +10874,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Ifo ExpectationsFEB</t>
+          <t>Ifo Current ConditionsFEB</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -10901,22 +10901,22 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>CPI FinalJAN</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -10963,18 +10963,18 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>CPI FinalJAN</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G383" t="n">
@@ -10994,22 +10994,22 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate MoMFEB</t>
+          <t>Mid-month Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mid-month Inflation Rate MoMFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>12-Month BTF Auction</t>
+          <t>3-Month BTF Auction</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>3-Month BTF Auction</t>
+          <t>12-Month BTF Auction</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -11580,6 +11580,118 @@
         <v>3</v>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2025-02-25 12:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="G409" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2025-02-25 12:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>GDP Growth Rate YoY FinalQ4</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="G410" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2025-02-25 12:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>New Car Registrations YoYJAN</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2025-02-25 12:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="G412" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1323,22 +1323,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1358,26 +1358,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1428,26 +1428,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1773,18 +1773,18 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -1804,22 +1804,26 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1830,27 +1834,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1870,26 +1870,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1935,23 +1935,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2006,26 +2006,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2036,23 +2036,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2067,12 +2071,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2082,16 +2086,16 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -2107,22 +2111,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2173,22 +2173,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2204,22 +2208,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2239,18 +2243,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2270,22 +2274,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2305,26 +2309,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">

--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G418"/>
+  <dimension ref="A1:G421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1323,22 +1323,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1358,26 +1358,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1393,26 +1393,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1428,22 +1428,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1773,22 +1773,18 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -1803,23 +1799,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -1834,23 +1830,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1870,26 +1870,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1950,16 +1950,16 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2010,26 +2010,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2040,27 +2040,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2080,18 +2076,18 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2111,22 +2107,26 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2173,22 +2173,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2204,22 +2208,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2239,18 +2243,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2270,22 +2274,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2305,26 +2309,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -2575,19 +2575,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wholesale Prices YoYJAN</t>
+          <t>Vehicle Sales YoYJAN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2605,18 +2605,18 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2634,18 +2634,18 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -2658,19 +2658,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vehicle Sales YoYJAN</t>
+          <t>Wholesale Prices YoYJAN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2719,22 +2719,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ PrelQ4</t>
+          <t>GDP External Demand QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GDP Growth Annualized PrelQ4</t>
+          <t>GDP Growth Rate QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GDP Capital Expenditure QoQ PrelQ4</t>
+          <t>GDP Growth Annualized PrelQ4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2792,11 +2792,11 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -2812,18 +2812,18 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GDP External Demand QoQ PrelQ4</t>
+          <t>GDP Capital Expenditure QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -2870,18 +2870,18 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Non-Oil Exports YoYJAN</t>
+          <t>Non-Oil Exports MoMJAN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -2901,18 +2901,18 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Non-Oil Exports MoMJAN</t>
+          <t>Non-Oil Exports YoYJAN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3187,10 +3187,14 @@
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>€4.35B</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>€ -4.9B</t>
+          <t>€4.5B</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -3205,7 +3209,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3214,14 +3218,10 @@
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>€4.35B</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>€4.5B</t>
+          <t>€ -4.9B</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -3578,17 +3578,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>European Commission Winter Forecasts</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>$-24.0B</t>
+        </is>
+      </c>
       <c r="G105" t="n">
         <v>2</v>
       </c>
@@ -3601,21 +3605,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>European Commission Winter Forecasts</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>$-24.0B</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
         <v>2</v>
       </c>
@@ -3628,17 +3628,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Eurogroup Meeting</t>
+          <t>Budget BalanceJAN</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>TRY-150.0B</t>
+        </is>
+      </c>
       <c r="G107" t="n">
         <v>2</v>
       </c>
@@ -3651,21 +3655,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Auto Sales YoYJAN</t>
+          <t>Eurogroup Meeting</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
         <v>2</v>
       </c>
@@ -3710,14 +3710,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Budget BalanceJAN</t>
+          <t>Auto Sales YoYJAN</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>TRY-150.0B</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -4227,14 +4227,18 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ PrelQ4</t>
+          <t>Labour Productivity QoQ FinalQ3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4254,18 +4258,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Labour Productivity QoQ FinalQ3</t>
+          <t>Labour Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4308,18 +4308,18 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Unemployment RateQ4</t>
+          <t>Unemployed PersonsQ4</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>8.1M</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -4335,18 +4335,18 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Unemployed PersonsQ4</t>
+          <t>Unemployment RateQ4</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>8.1M</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -4523,27 +4523,23 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -4559,22 +4555,18 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CPI Trimmed-Mean YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
@@ -4590,18 +4582,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CPI Median YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -4621,14 +4609,18 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPI Median YoYJAN</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -4648,18 +4640,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI Trimmed-Mean YoYJAN</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -4670,23 +4666,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -4751,19 +4751,19 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bundesbank Balz Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4774,19 +4774,19 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Bundesbank Balz Speech</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
@@ -4894,14 +4894,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -4917,14 +4917,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
@@ -5036,22 +5036,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Imports YoYJAN</t>
+          <t>Machinery Orders YoYDEC</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -5067,22 +5067,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Machinery Orders YoYDEC</t>
+          <t>Imports YoYJAN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -5218,12 +5218,20 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>RBA Chart Pack</t>
+          <t>Wage Price Index YoYQ4</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="G166" t="n">
         <v>3</v>
       </c>
@@ -5241,20 +5249,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Wage Price Index QoQQ4</t>
+          <t>RBA Chart Pack</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
       <c r="G167" t="n">
         <v>3</v>
       </c>
@@ -5272,18 +5272,18 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Wage Price Index YoYQ4</t>
+          <t>Wage Price Index QoQQ4</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -5353,18 +5353,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PPI Output MoMJAN</t>
+          <t>PPI Output YoYJAN</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
         <is>
           <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5384,14 +5380,18 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PPI Input YoYJAN</t>
+          <t>PPI Output MoMJAN</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5500,14 +5500,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PPI Output YoYJAN</t>
+          <t>PPI Input YoYJAN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -5554,14 +5554,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PPI Core Output MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -5581,18 +5581,18 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -5608,14 +5608,18 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -5635,22 +5639,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -5666,22 +5670,18 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>PPI Core Output MoMJAN</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -5724,22 +5724,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Interest Rate Decision</t>
+          <t>Lending Facility RateFEB</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -5755,22 +5755,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Deposit Facility RateFEB</t>
+          <t>Interest Rate Decision</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -5786,18 +5786,18 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Lending Facility RateFEB</t>
+          <t>Deposit Facility RateFEB</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -5812,21 +5812,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>ECB Non-Monetary Policy Meeting</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
         <v>3</v>
       </c>
@@ -5844,7 +5840,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -5855,7 +5851,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5893,17 +5889,21 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ECB Non-Monetary Policy Meeting</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G190" t="n">
         <v>3</v>
       </c>
@@ -5921,18 +5921,18 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192">
@@ -5948,14 +5948,18 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Current AccountDEC</t>
+          <t>Current Account s.aDEC</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>€30B</t>
+        </is>
+      </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>€32B</t>
+          <t>€30B</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -5975,18 +5979,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Current Account s.aDEC</t>
+          <t>Current AccountDEC</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>€30B</t>
-        </is>
-      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>€30B</t>
+          <t>€32B</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -6248,14 +6248,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -6294,14 +6294,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="207">
@@ -6317,18 +6317,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -6344,22 +6348,18 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -6375,18 +6375,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -6402,22 +6406,18 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
@@ -6582,19 +6582,19 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Consumer ConfidenceJAN</t>
+          <t>Leading Indicator MoMJAN</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -6609,17 +6609,21 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual Budget Speech</t>
+          <t>Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
       <c r="G218" t="n">
         <v>3</v>
       </c>
@@ -6632,21 +6636,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Leading Indicator MoMJAN</t>
+          <t>Annual Budget Speech</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="n">
         <v>3</v>
       </c>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentFEB/15</t>
+          <t>Stock Investment by ForeignersFEB/15</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Stock Investment by ForeignersFEB/15</t>
+          <t>Foreign Bond InvestmentFEB/15</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -6883,18 +6883,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Full Time Employment ChgJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>33.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -6910,22 +6914,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Employment ChangeJAN</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>20K</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>23.0K</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
@@ -6941,22 +6945,18 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Part Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-10.0K</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232">
@@ -6972,22 +6972,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Employment ChangeJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>20K</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>23.0K</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233">
@@ -7003,18 +7003,18 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Part Time Employment ChgJAN</t>
+          <t>Full Time Employment ChgJAN</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>-10.0K</t>
+          <t>33.0K</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>3-Year Bonos Auction</t>
+          <t>5-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>5-Year Bonos Auction</t>
+          <t>3-Year Bonos Auction</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -7310,17 +7310,21 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>5-Year OAT Auction</t>
+          <t>Construction Output YoYDEC</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="G245" t="n">
         <v>3</v>
       </c>
@@ -7338,7 +7342,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>4-Year OAT Auction</t>
+          <t>3-Year OAT Auction</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -7361,7 +7365,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>3-Year OAT Auction</t>
+          <t>4-Year OAT Auction</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -7379,21 +7383,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Construction Output YoYDEC</t>
+          <t>5-Year OAT Auction</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+      <c r="F248" t="inlineStr"/>
       <c r="G248" t="n">
         <v>3</v>
       </c>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>11-Year Index-Linked OAT Auction</t>
+          <t>6-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>6-Year Index-Linked OAT Auction</t>
+          <t>11-Year Index-Linked OAT Auction</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -7475,17 +7475,21 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>7-Year OATi Auction</t>
+          <t>Building Permits YoYDEC</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
       <c r="G252" t="n">
         <v>3</v>
       </c>
@@ -7498,23 +7502,27 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Building Permits YoYDEC</t>
+          <t>CBI Industrial Trends OrdersFEB</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -7525,27 +7533,19 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends OrdersFEB</t>
+          <t>7-Year OATi Auction</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>-25</t>
-        </is>
-      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
       <c r="G254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -7584,14 +7584,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -7611,14 +7611,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -7638,16 +7638,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="F258" t="inlineStr"/>
       <c r="G258" t="n">
         <v>3</v>
       </c>
@@ -7665,7 +7661,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -7688,7 +7684,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -7711,7 +7707,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -7734,7 +7730,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -7757,14 +7753,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -7784,12 +7780,16 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="G264" t="n">
         <v>3</v>
       </c>
@@ -7833,23 +7833,27 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G266" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267">
@@ -7865,18 +7869,18 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Raw Materials Prices YoYJAN</t>
+          <t>New Housing Price Index YoYJAN</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
@@ -7919,18 +7923,18 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>New Housing Price Index MoMJAN</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -7941,27 +7945,23 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Raw Materials Prices YoYJAN</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7977,18 +7977,18 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>New Housing Price Index YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -8004,18 +8004,18 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>New Housing Price Index MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -8076,25 +8076,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMJAN</t>
+          <t>Monetary Policy Meeting Minutes</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
       <c r="G275" t="n">
         <v>3</v>
       </c>
@@ -8107,17 +8099,25 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Monetary Policy Meeting Minutes</t>
+          <t>CB Leading Index MoMJAN</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="G276" t="n">
         <v>3</v>
       </c>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>10-Year NTN-F Auction</t>
+          <t>2-Year LTN Auction</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2-Year LTN Auction</t>
+          <t>10-Year NTN-F Auction</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -8749,18 +8749,18 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -8776,14 +8776,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -8803,18 +8803,18 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>S&amp;P Global Australia Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Australia Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8880,18 +8880,18 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -8907,18 +8907,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310">
@@ -8934,14 +8938,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -8961,22 +8965,18 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate Ex-Food and Energy YoYJAN</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -9023,18 +9023,18 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Jibun Bank Services PMI FlashFEB</t>
+          <t>Jibun Bank Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -9050,18 +9050,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Jibun Bank Composite PMI FlashFEB</t>
+          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -9077,18 +9081,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Jibun Bank Manufacturing PMI FlashFEB</t>
+          <t>Jibun Bank Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9212,14 +9212,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel YoYJAN</t>
+          <t>Retail Sales ex Fuel MoMJAN</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -9239,14 +9239,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Retail Sales ex Fuel MoMJAN</t>
+          <t>Retail Sales ex Fuel YoYJAN</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -9266,18 +9266,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Public Sector Net Borrowing Ex BanksJAN</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>£20.5B</t>
+        </is>
+      </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>£19.0B</t>
         </is>
       </c>
       <c r="G322" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="323">
@@ -9293,22 +9297,18 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Public Sector Net Borrowing Ex BanksJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>£20.5B</t>
-        </is>
-      </c>
+      <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
-          <t>£19.0B</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="324">
@@ -9432,18 +9432,18 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -9490,18 +9490,18 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -9521,22 +9521,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -9552,14 +9552,18 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -9579,22 +9583,18 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>45.5</t>
-        </is>
-      </c>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -9610,18 +9610,18 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate YoY FinalJAN</t>
+          <t>Harmonised Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -9641,18 +9641,18 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Harmonised Inflation Rate MoM FinalJAN</t>
+          <t>Harmonised Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -9698,23 +9698,23 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Inflation Rate MoM FinalJAN</t>
+          <t>HCOB Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -9729,23 +9729,23 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>HCOB Services PMI FlashFEB</t>
+          <t>Inflation Rate MoM FinalJAN</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -9765,18 +9765,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>HCOB Manufacturing PMI FlashFEB</t>
+          <t>HCOB Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+      <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -9796,14 +9792,18 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>HCOB Composite PMI FlashFEB</t>
+          <t>HCOB Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -10016,18 +10016,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Economic Activity MoMDEC</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="349">
@@ -10043,22 +10047,18 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>Economic Activity MoMDEC</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
+      <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="350">
@@ -10325,18 +10325,18 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -10356,22 +10356,22 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="G360" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="361">
@@ -10387,22 +10387,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="G361" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -10418,22 +10418,18 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
@@ -10449,22 +10445,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="364">
@@ -10480,18 +10476,22 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
-      <c r="E364" t="inlineStr"/>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -10548,17 +10548,21 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Federal Tax RevenuesJAN</t>
+          <t>FDI (YTD) YoYJAN</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-18.0%</t>
+        </is>
+      </c>
       <c r="G367" t="n">
         <v>3</v>
       </c>
@@ -10571,21 +10575,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>FDI (YTD) YoYJAN</t>
+          <t>Federal Tax RevenuesJAN</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>-18.0%</t>
-        </is>
-      </c>
+      <c r="F368" t="inlineStr"/>
       <c r="G368" t="n">
         <v>3</v>
       </c>
@@ -10693,14 +10693,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G373" t="n">
@@ -10720,14 +10720,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="G374" t="n">
@@ -10747,14 +10747,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G375" t="n">
@@ -10901,22 +10901,22 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Inflation Rate YoY FinalJAN</t>
+          <t>CPI FinalJAN</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>126.71</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -10932,22 +10932,22 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoY FinalJAN</t>
+          <t>Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -10963,18 +10963,18 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>CPI FinalJAN</t>
+          <t>Core Inflation Rate YoY FinalJAN</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G383" t="n">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>3-Month Bubill Auction</t>
+          <t>9-Month Bubill Auction</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>9-Month Bubill Auction</t>
+          <t>3-Month Bubill Auction</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate YoYFEB</t>
+          <t>Mid-month Core Inflation Rate MoMFEB</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mid-month Core Inflation Rate MoMFEB</t>
+          <t>Mid-month Core Inflation Rate YoYFEB</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -11438,12 +11438,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>20-Year KTB Auction</t>
+          <t>MAS 12-Week Bill Auction</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>MAS 12-Week Bill Auction</t>
+          <t>MAS 4-Week Bill Auction</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -11484,12 +11484,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>MAS 4-Week Bill Auction</t>
+          <t>20-Year KTB Auction</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -11512,14 +11512,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr">
         <is>
-          <t>SAR 34B</t>
+          <t>SAR 60.5B</t>
         </is>
       </c>
       <c r="G406" t="n">
@@ -11539,14 +11539,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
-          <t>SAR 94.5B</t>
+          <t>SAR 34B</t>
         </is>
       </c>
       <c r="G407" t="n">
@@ -11566,14 +11566,14 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr">
         <is>
-          <t>SAR 60.5B</t>
+          <t>SAR 94.5B</t>
         </is>
       </c>
       <c r="G408" t="n">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ FinalQ4</t>
+          <t>GDP Growth Rate YoY FinalQ4</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -11619,17 +11619,25 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>New Car Registrations YoYJAN</t>
+          <t>GDP Growth Rate QoQ FinalQ4</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
       <c r="G410" t="n">
         <v>2</v>
       </c>
@@ -11642,27 +11650,23 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>GDP Growth Rate YoY FinalQ4</t>
+          <t>Leading Business Cycle Indicator MoMDEC</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
+      <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -11673,23 +11677,19 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Leading Business Cycle Indicator MoMDEC</t>
+          <t>New Car Registrations YoYJAN</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>BTP€i Auction</t>
+          <t>2-Year BTP Short Term Auction</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -11723,17 +11723,21 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2-Year BTP Short Term Auction</t>
+          <t>Negotiated Wage GrowthQ4</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G414" t="n">
         <v>3</v>
       </c>
@@ -11746,21 +11750,17 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Negotiated Wage GrowthQ4</t>
+          <t>BTP€i Auction</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>5.1%</t>
-        </is>
-      </c>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
         <v>3</v>
       </c>
@@ -11842,6 +11842,79 @@
         <v>2</v>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2025-02-25 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>IPCA mid-month CPI YoYFEB</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2025-02-25 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>IPCA mid-month CPI MoMFEB</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2025-02-25 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Negotiated Wage GrowthQ4</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="G421" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_All Countries_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -873,12 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5-Year JGB Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.982%</t>
+          <t>0.3098%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year JGB Auction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.3098%</t>
+          <t>0.982%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1323,22 +1323,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Total Social FinancingJAN</t>
+          <t>M2 Money Supply YoYJAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CNY7060B</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CNY6400B</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CNY6200.0B</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1358,26 +1358,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Outstanding Loan Growth YoYJAN</t>
+          <t>New Yuan LoansJAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>CNY5130B</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>CNY800B</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>CNY1000.0B</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1393,26 +1393,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New Yuan LoansJAN</t>
+          <t>Total Social FinancingJAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CNY5130B</t>
+          <t>CNY7060B</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CNY800B</t>
+          <t>CNY6400B</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CNY1000.0B</t>
+          <t>CNY6200.0B</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1428,22 +1428,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M2 Money Supply YoYJAN</t>
+          <t>Outstanding Loan Growth YoYJAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Manufacturing Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1783,16 +1783,16 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1808,22 +1808,18 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Manufacturing Sales MoM FinalDEC</t>
+          <t>New Motor Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>135.5K</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>153K</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -1838,23 +1834,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Wholesale Sales MoM FinalDEC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.7%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1874,26 +1874,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1944,22 +1944,26 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1975,12 +1979,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1990,7 +1994,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2010,26 +2014,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2040,27 +2044,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wholesale Sales MoM FinalDEC</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2075,23 +2075,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New Motor Vehicle SalesDEC</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>135.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>153K</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2111,18 +2111,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2173,26 +2173,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2208,18 +2208,18 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2239,22 +2239,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2274,22 +2270,26 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2305,22 +2305,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G59" t="n">
